--- a/config/yunying/reunion_catchup.xlsx
+++ b/config/yunying/reunion_catchup.xlsx
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン回数増加</t>
+          <t>地牢次数增加</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンの回数が増加</t>
+          <t>活动中，地牢次数增加</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベントが効果を発揮します。2つイベントにバフ回数がある場合、そのイベントのダンジョンではイベント回数が重複します。</t>
+          <t>与通常活动同时举行时，两个活动都会发挥效果。如果两个活动都有增益次数，则该活动的地牢将重复活动次数。</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>試練の旅掃討が2倍</t>
+          <t>试炼之旅扫荡2倍</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>イベント中、試練の旅の掃討報酬2倍</t>
+          <t>活动中，试炼之旅的扫荡奖励2倍</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベント倍率や時間などの条件は重複しませんのでご注意ください。</t>
+          <t>请注意，与通常活动同时举行时，两个活动的倍率和时间等条件不会重复。</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>ストーリーダンジョンを2倍ドロップ</t>
+          <t>故事地下城下降2倍</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンのドロップが2倍</t>
+          <t>活动期间，地下城掉落双倍</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>掃討と戦闘のどちらもカウントに含まれます。日常任務の2増イベントと同時開催中、通常イベントの時間に基づいて計算し、その後イベント回数が反映されます。</t>
+          <t>扫荡和战斗都包括在计数中。日常任务的2增加活动同时进行时，以通常活动的时间为基础进行计算，然后反映活动次数。</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>スタミナ購入2倍</t>
+          <t>购买2倍耐力</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>イベント中、スタミナ購入5回までスタミナを2倍獲得</t>
+          <t>活动中，购买5次体力可获得2倍体力</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>日常スタミナ購入の2増イベントと同時開催中、購入回数が多い方のイベントが適用されます。</t>
+          <t>日常体力购入的2增活动同时举行中，购入次数多的活动将适用。</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>金貨回収2倍</t>
+          <t>金币回收2倍</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>イベント中、金貨回収8回まで2倍報酬獲得</t>
+          <t>活动中，金币回收8次可获得2倍奖励</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>日常の金貨開通2増イベントと同時開催中、倍増回数が多い方のイベントが適用されます。</t>
+          <t>日常金币开通2增活动同时举行中，倍增次数多的活动适用。</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン回数増加</t>
+          <t>地牢次数增加</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンの回数が増加</t>
+          <t>活动中，地牢次数增加</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベントが効果を発揮します。2つイベントにバフ回数がある場合、そのイベントのダンジョンではイベント回数が重複します。</t>
+          <t>与通常活动同时举行时，两个活动都会发挥效果。如果两个活动都有增益次数，则该活动的地牢将重复活动次数。</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>試練の旅掃討が2倍</t>
+          <t>试炼之旅扫荡2倍</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>イベント中、試練の旅の掃討報酬2倍</t>
+          <t>活动中，试炼之旅的扫荡奖励2倍</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベント倍率や時間などの条件は重複しませんのでご注意ください。</t>
+          <t>请注意，与通常活动同时举行时，两个活动的倍率和时间等条件不会重复。</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>ストーリーダンジョンを2倍ドロップ</t>
+          <t>故事地下城下降2倍</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンのドロップが2倍</t>
+          <t>活动期间，地下城掉落双倍</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>掃討と戦闘のどちらもカウントに含まれます。日常任務の2増イベントと同時開催中、通常イベントの時間に基づいて計算し、その後イベント回数が反映されます。</t>
+          <t>扫荡和战斗都包括在计数中。日常任务的2增加活动同时进行时，以通常活动的时间为基础进行计算，然后反映活动次数。</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>スタミナ購入2倍</t>
+          <t>购买2倍耐力</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>イベント中、スタミナ購入5回までスタミナを2倍獲得</t>
+          <t>活动中，购买5次体力可获得2倍体力</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>日常スタミナ購入の2増イベントと同時開催中、購入回数が多い方のイベントが適用されます。</t>
+          <t>日常体力购入的2增活动同时举行中，购入次数多的活动将适用。</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>金貨回収2倍</t>
+          <t>金币回收2倍</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>イベント中、金貨回収8回まで2倍報酬獲得</t>
+          <t>活动中，金币回收8次可获得2倍奖励</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>日常の金貨開通2増イベントと同時開催中、倍増回数が多い方のイベントが適用されます。</t>
+          <t>日常金币开通2增活动同时举行中，倍增次数多的活动适用。</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン回数増加</t>
+          <t>地牢次数增加</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンの回数が増加</t>
+          <t>活动中，地牢次数增加</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベントが効果を発揮します。2つイベントにバフ回数がある場合、そのイベントのダンジョンではイベント回数が重複します。</t>
+          <t>与通常活动同时举行时，两个活动都会发挥效果。如果两个活动都有增益次数，则该活动的地牢将重复活动次数。</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>試練の旅掃討が2倍</t>
+          <t>试炼之旅扫荡2倍</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>イベント中、試練の旅の掃討報酬2倍</t>
+          <t>活动中，试炼之旅的扫荡奖励2倍</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベント倍率や時間などの条件は重複しませんのでご注意ください。</t>
+          <t>请注意，与通常活动同时举行时，两个活动的倍率和时间等条件不会重复。</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>ストーリーダンジョンを2倍ドロップ</t>
+          <t>故事地下城下降2倍</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンのドロップが2倍</t>
+          <t>活动期间，地下城掉落双倍</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>掃討と戦闘のどちらもカウントに含まれます。日常任務の2増イベントと同時開催中、通常イベントの時間に基づいて計算し、その後イベント回数が反映されます。</t>
+          <t>扫荡和战斗都包括在计数中。日常任务的2增加活动同时进行时，以通常活动的时间为基础进行计算，然后反映活动次数。</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>スタミナ購入2倍</t>
+          <t>购买2倍耐力</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>イベント中、スタミナ購入5回までスタミナを2倍獲得</t>
+          <t>活动中，购买5次体力可获得2倍体力</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>日常スタミナ購入の2増イベントと同時開催中、購入回数が多い方のイベントが適用されます。</t>
+          <t>日常体力购入的2增活动同时举行中，购入次数多的活动将适用。</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>金貨回収2倍</t>
+          <t>金币回收2倍</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>イベント中、金貨回収8回まで2倍報酬獲得</t>
+          <t>活动中，金币回收8次可获得2倍奖励</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>日常の金貨開通2増イベントと同時開催中、倍増回数が多い方のイベントが適用されます。</t>
+          <t>日常金币开通2增活动同时举行中，倍增次数多的活动适用。</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン回数増加</t>
+          <t>地牢次数增加</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンの回数が増加</t>
+          <t>活动中，地牢次数增加</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベントが効果を発揮します。2つイベントにバフ回数がある場合、そのイベントのダンジョンではイベント回数が重複します。</t>
+          <t>与通常活动同时举行时，两个活动都会发挥效果。如果两个活动都有增益次数，则该活动的地牢将重复活动次数。</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>試練の旅掃討が2倍</t>
+          <t>试炼之旅扫荡2倍</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>イベント中、試練の旅の掃討報酬2倍</t>
+          <t>活动中，试炼之旅的扫荡奖励2倍</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベント倍率や時間などの条件は重複しませんのでご注意ください。</t>
+          <t>请注意，与通常活动同时举行时，两个活动的倍率和时间等条件不会重复。</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>ストーリーダンジョンを2倍ドロップ</t>
+          <t>故事地下城下降2倍</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンのドロップが2倍</t>
+          <t>活动期间，地下城掉落双倍</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="M24" s="1" t="inlineStr">
         <is>
-          <t>掃討と戦闘のどちらもカウントに含まれます。日常任務の2増イベントと同時開催中、通常イベントの時間に基づいて計算し、その後イベント回数が反映されます。</t>
+          <t>扫荡和战斗都包括在计数中。日常任务的2增加活动同时进行时，以通常活动的时间为基础进行计算，然后反映活动次数。</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>スタミナ購入2倍</t>
+          <t>购买2倍耐力</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>イベント中、スタミナ購入5回までスタミナを2倍獲得</t>
+          <t>活动中，购买5次体力可获得2倍体力</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="M25" s="1" t="inlineStr">
         <is>
-          <t>日常スタミナ購入の2増イベントと同時開催中、購入回数が多い方のイベントが適用されます。</t>
+          <t>日常体力购入的2增活动同时举行中，购入次数多的活动将适用。</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>金貨回収2倍</t>
+          <t>金币回收2倍</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>イベント中、金貨回収10回まで2倍報酬獲得</t>
+          <t>活动中，金币回收10次可获得2倍奖励</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
-          <t>日常の金貨開通2増イベントと同時開催中、倍増回数が多い方のイベントが適用されます。</t>
+          <t>日常金币开通2增活动同时举行中，倍增次数多的活动适用。</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン回数増加</t>
+          <t>地牢次数增加</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンの回数が増加</t>
+          <t>活动中，地牢次数增加</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベントが効果を発揮します。2つイベントにバフ回数がある場合、そのイベントのダンジョンではイベント回数が重複します。</t>
+          <t>与通常活动同时举行时，两个活动都会发挥效果。如果两个活动都有增益次数，则该活动的地牢将重复活动次数。</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>試練の旅掃討が2倍</t>
+          <t>试炼之旅扫荡2倍</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>イベント中、試練の旅の掃討報酬2倍</t>
+          <t>活动中，试炼之旅的扫荡奖励2倍</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベント倍率や時間などの条件は重複しませんのでご注意ください。</t>
+          <t>请注意，与通常活动同时举行时，两个活动的倍率和时间等条件不会重复。</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ストーリーダンジョンを2倍ドロップ</t>
+          <t>故事地下城下降2倍</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンのドロップが2倍</t>
+          <t>活动期间，地下城掉落双倍</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
-          <t>掃討と戦闘のどちらもカウントに含まれます。日常任務の2増イベントと同時開催中、通常イベントの時間に基づいて計算し、その後イベント回数が反映されます。</t>
+          <t>扫荡和战斗都包括在计数中。日常任务的2增加活动同时进行时，以通常活动的时间为基础进行计算，然后反映活动次数。</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>スタミナ購入2倍</t>
+          <t>购买2倍耐力</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>イベント中、スタミナ購入5回までスタミナを2倍獲得</t>
+          <t>活动中，购买5次体力可获得2倍体力</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
-          <t>日常スタミナ購入の2増イベントと同時開催中、購入回数が多い方のイベントが適用されます。</t>
+          <t>日常体力购入的2增活动同时举行中，购入次数多的活动将适用。</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>金貨回収2倍</t>
+          <t>金币回收2倍</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>イベント中、金貨回収10回まで2倍報酬獲得</t>
+          <t>活动中，金币回收10次可获得2倍奖励</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="M32" s="1" t="inlineStr">
         <is>
-          <t>日常の金貨開通2増イベントと同時開催中、倍増回数が多い方のイベントが適用されます。</t>
+          <t>日常金币开通2增活动同时举行中，倍增次数多的活动适用。</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン回数増加</t>
+          <t>地牢次数增加</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンの回数が増加</t>
+          <t>活动中，地牢次数增加</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベントが効果を発揮します。2つイベントにバフ回数がある場合、そのイベントのダンジョンではイベント回数が重複します。</t>
+          <t>与通常活动同时举行时，两个活动都会发挥效果。如果两个活动都有增益次数，则该活动的地牢将重复活动次数。</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>試練の旅掃討が2倍</t>
+          <t>试炼之旅扫荡2倍</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>イベント中、試練の旅の掃討報酬2倍</t>
+          <t>活动中，试炼之旅的扫荡奖励2倍</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M35" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベント倍率や時間などの条件は重複しませんのでご注意ください。</t>
+          <t>请注意，与通常活动同时举行时，两个活动的倍率和时间等条件不会重复。</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>ストーリーダンジョンを2倍ドロップ</t>
+          <t>故事地下城下降2倍</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンのドロップが2倍</t>
+          <t>活动期间，地下城掉落双倍</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
-          <t>掃討と戦闘のどちらもカウントに含まれます。日常任務の2増イベントと同時開催中、通常イベントの時間に基づいて計算し、その後イベント回数が反映されます。</t>
+          <t>扫荡和战斗都包括在计数中。日常任务的2增加活动同时进行时，以通常活动的时间为基础进行计算，然后反映活动次数。</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>スタミナ購入2倍</t>
+          <t>购买2倍耐力</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>イベント中、スタミナ購入5回までスタミナを2倍獲得</t>
+          <t>活动中，购买5次体力可获得2倍体力</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="M37" s="1" t="inlineStr">
         <is>
-          <t>日常スタミナ購入の2増イベントと同時開催中、購入回数が多い方のイベントが適用されます。</t>
+          <t>日常体力购入的2增活动同时举行中，购入次数多的活动将适用。</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>金貨回収2倍</t>
+          <t>金币回收2倍</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>イベント中、金貨回収10回まで2倍報酬獲得</t>
+          <t>活动中，金币回收10次可获得2倍奖励</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="M38" s="1" t="inlineStr">
         <is>
-          <t>日常の金貨開通2増イベントと同時開催中、倍増回数が多い方のイベントが適用されます。</t>
+          <t>日常金币开通2增活动同时举行中，倍增次数多的活动适用。</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ダンジョン回数増加加</t>
+          <t>增加地牢次数</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンの回数が増加</t>
+          <t>活动中，地牢次数增加</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="M40" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベントが効果を発揮します。2つイベントにバフ回数がある場合、そのイベントのダンジョンではイベント回数が重複します。</t>
+          <t>与通常活动同时举行时，两个活动都会发挥效果。如果两个活动都有增益次数，则该活动的地牢将重复活动次数。</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>試練の旅掃討が2倍</t>
+          <t>试炼之旅扫荡2倍</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>イベント中、試練の旅の掃討報酬2倍</t>
+          <t>活动中，试炼之旅的扫荡奖励2倍</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M41" s="1" t="inlineStr">
         <is>
-          <t>通常イベントと同時開催中、2つのイベント倍率や時間などの条件は重複しませんのでご注意ください。</t>
+          <t>请注意，与通常活动同时举行时，两个活动的倍率和时间等条件不会重复。</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ストーリーダンジョンを2倍ドロップ</t>
+          <t>故事地下城下降2倍</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>イベント中、ダンジョンのドロップが2倍</t>
+          <t>活动期间，地下城掉落双倍</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="M42" s="1" t="inlineStr">
         <is>
-          <t>掃討と戦闘のどちらもカウントに含まれます。日常任務の2増イベントと同時開催中、通常イベントの時間に基づいて計算し、その後イベント回数が反映されます。</t>
+          <t>扫荡和战斗都包括在计数中。日常任务的2增加活动同时进行时，以通常活动的时间为基础进行计算，然后反映活动次数。</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>スタミナ購入2倍</t>
+          <t>购买2倍耐力</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>イベント中、スタミナ購入5回までスタミナを2倍獲得</t>
+          <t>活动中，购买5次体力可获得2倍体力</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
-          <t>日常スタミナ購入の2増イベントと同時開催中、購入回数が多い方のイベントが適用されます。</t>
+          <t>日常体力购入的2增活动同时举行中，购入次数多的活动将适用。</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>金貨回収2倍</t>
+          <t>金币回收2倍</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>イベント中、金貨回収10回まで2倍報酬獲得</t>
+          <t>活动中，金币回收10次可获得2倍奖励</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="M44" s="1" t="inlineStr">
         <is>
-          <t>日常の金貨開通2増イベントと同時開催中、倍増回数が多い方のイベントが適用されます。</t>
+          <t>日常金币开通2增活动同时举行中，倍增次数多的活动适用。</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
